--- a/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
+++ b/datasets/datasets_aumentados/logs/pcsmote/por_muestras/log_pcsmote_x_muestra_wdbc.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnatello\Documents\GitHub\etapa-analisis_pcsmote\datasets\datasets_aumentados\logs\pcsmote\por_muestras\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FamiliaNatelloMedina\Desktop\codigo\datasets\datasets_aumentados\logs\pcsmote\por_muestras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED859240-24B7-45FB-931C-9B75D236BF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -153,7 +152,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -307,23 +306,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -359,23 +341,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -551,8 +516,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y841"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -637,7 +601,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -708,7 +672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -779,7 +743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -850,7 +814,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -921,7 +885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -992,7 +956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1063,7 +1027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1134,7 +1098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1205,7 +1169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1276,7 +1240,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1347,7 +1311,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1418,7 +1382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1489,7 +1453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1560,7 +1524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1631,7 +1595,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1702,7 +1666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1773,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1844,7 +1808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1915,7 +1879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1986,7 +1950,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2057,7 +2021,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2128,7 +2092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2199,7 +2163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2270,7 +2234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2341,7 +2305,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2412,7 +2376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2483,7 +2447,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2554,7 +2518,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2625,7 +2589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2696,7 +2660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -2767,7 +2731,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -2838,7 +2802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -2909,7 +2873,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -2980,7 +2944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3051,7 +3015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -3122,7 +3086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3193,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -3264,7 +3228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -3335,7 +3299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -3406,7 +3370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3477,7 +3441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3548,7 +3512,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -3619,7 +3583,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -3690,7 +3654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -3761,7 +3725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -3832,7 +3796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -3903,7 +3867,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -3974,7 +3938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -4045,7 +4009,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -4116,7 +4080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -4187,7 +4151,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -4258,7 +4222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -4329,7 +4293,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -4400,7 +4364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -4471,7 +4435,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -4542,7 +4506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -4613,7 +4577,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -4684,7 +4648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -4755,7 +4719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -4826,7 +4790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>25</v>
       </c>
@@ -4897,7 +4861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -4968,7 +4932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -5039,7 +5003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -5110,7 +5074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -5181,7 +5145,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -5252,7 +5216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -5323,7 +5287,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -5394,7 +5358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -5465,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -5536,7 +5500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -5607,7 +5571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -5678,7 +5642,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -5749,7 +5713,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -5820,7 +5784,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -5891,7 +5855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -5962,7 +5926,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -6033,7 +5997,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -6104,7 +6068,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -6175,7 +6139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -6246,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -6317,7 +6281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -6388,7 +6352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -6459,7 +6423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -6530,7 +6494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -6601,7 +6565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -6672,7 +6636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -6743,7 +6707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -6814,7 +6778,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -6885,7 +6849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -6956,7 +6920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -7027,7 +6991,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -7098,7 +7062,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -7169,7 +7133,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -7240,7 +7204,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -7311,7 +7275,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -7382,7 +7346,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -7453,7 +7417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -7524,7 +7488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -7595,7 +7559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>25</v>
       </c>
@@ -7666,7 +7630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>25</v>
       </c>
@@ -7737,7 +7701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>25</v>
       </c>
@@ -7808,7 +7772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>25</v>
       </c>
@@ -7879,7 +7843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>25</v>
       </c>
@@ -7950,7 +7914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>25</v>
       </c>
@@ -8021,7 +7985,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>25</v>
       </c>
@@ -8092,7 +8056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>25</v>
       </c>
@@ -8163,7 +8127,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>25</v>
       </c>
@@ -8234,7 +8198,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>25</v>
       </c>
@@ -8305,7 +8269,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>25</v>
       </c>
@@ -8376,7 +8340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>25</v>
       </c>
@@ -8447,7 +8411,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -8518,7 +8482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -8589,7 +8553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>25</v>
       </c>
@@ -8660,7 +8624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>25</v>
       </c>
@@ -8731,7 +8695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>25</v>
       </c>
@@ -8802,7 +8766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>25</v>
       </c>
@@ -8873,7 +8837,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>25</v>
       </c>
@@ -8944,7 +8908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>25</v>
       </c>
@@ -9015,7 +8979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>25</v>
       </c>
@@ -9086,7 +9050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>25</v>
       </c>
@@ -9157,7 +9121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>25</v>
       </c>
@@ -9228,7 +9192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>25</v>
       </c>
@@ -9299,7 +9263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>25</v>
       </c>
@@ -9370,7 +9334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>25</v>
       </c>
@@ -9441,7 +9405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>25</v>
       </c>
@@ -9512,7 +9476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>25</v>
       </c>
@@ -9583,7 +9547,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>25</v>
       </c>
@@ -9654,7 +9618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>25</v>
       </c>
@@ -9725,7 +9689,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>25</v>
       </c>
@@ -9796,7 +9760,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>25</v>
       </c>
@@ -9867,7 +9831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>25</v>
       </c>
@@ -9938,7 +9902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>25</v>
       </c>
@@ -10009,7 +9973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>25</v>
       </c>
@@ -10080,7 +10044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>25</v>
       </c>
@@ -10151,7 +10115,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>25</v>
       </c>
@@ -10222,7 +10186,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>25</v>
       </c>
@@ -10293,7 +10257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>25</v>
       </c>
@@ -10364,7 +10328,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>25</v>
       </c>
@@ -10435,7 +10399,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>25</v>
       </c>
@@ -10506,7 +10470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>25</v>
       </c>
@@ -10577,7 +10541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>25</v>
       </c>
@@ -10648,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -10719,7 +10683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -10790,7 +10754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>25</v>
       </c>
@@ -10861,7 +10825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>25</v>
       </c>
@@ -10932,7 +10896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>25</v>
       </c>
@@ -11003,7 +10967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>25</v>
       </c>
@@ -11074,7 +11038,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>25</v>
       </c>
@@ -11145,7 +11109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>25</v>
       </c>
@@ -11216,7 +11180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>25</v>
       </c>
@@ -11287,7 +11251,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>25</v>
       </c>
@@ -11358,7 +11322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>25</v>
       </c>
@@ -11429,7 +11393,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>25</v>
       </c>
@@ -11500,7 +11464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>25</v>
       </c>
@@ -11571,7 +11535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>25</v>
       </c>
@@ -11642,7 +11606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>25</v>
       </c>
@@ -11713,7 +11677,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>25</v>
       </c>
@@ -11784,7 +11748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>25</v>
       </c>
@@ -11855,7 +11819,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>25</v>
       </c>
@@ -11926,7 +11890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>25</v>
       </c>
@@ -11997,7 +11961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>25</v>
       </c>
@@ -12068,7 +12032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>25</v>
       </c>
@@ -12139,7 +12103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>25</v>
       </c>
@@ -12210,7 +12174,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>25</v>
       </c>
@@ -12281,7 +12245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>25</v>
       </c>
@@ -12352,7 +12316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>25</v>
       </c>
@@ -12423,7 +12387,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>25</v>
       </c>
@@ -12494,7 +12458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>25</v>
       </c>
@@ -12565,7 +12529,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>25</v>
       </c>
@@ -12636,7 +12600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>25</v>
       </c>
@@ -12707,7 +12671,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>26</v>
       </c>
@@ -12778,7 +12742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>26</v>
       </c>
@@ -12849,7 +12813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>26</v>
       </c>
@@ -12920,7 +12884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>26</v>
       </c>
@@ -12991,7 +12955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>26</v>
       </c>
@@ -13062,7 +13026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>26</v>
       </c>
@@ -13133,7 +13097,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>26</v>
       </c>
@@ -13204,7 +13168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>26</v>
       </c>
@@ -13275,7 +13239,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>26</v>
       </c>
@@ -13346,7 +13310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>26</v>
       </c>
@@ -13417,7 +13381,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>26</v>
       </c>
@@ -13488,7 +13452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>26</v>
       </c>
@@ -13559,7 +13523,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>26</v>
       </c>
@@ -13630,7 +13594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>26</v>
       </c>
@@ -13701,7 +13665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>26</v>
       </c>
@@ -13772,7 +13736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>26</v>
       </c>
@@ -13843,7 +13807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>26</v>
       </c>
@@ -13914,7 +13878,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>26</v>
       </c>
@@ -13985,7 +13949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>26</v>
       </c>
@@ -14056,7 +14020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>26</v>
       </c>
@@ -14127,7 +14091,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>26</v>
       </c>
@@ -14198,7 +14162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>26</v>
       </c>
@@ -14269,7 +14233,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>26</v>
       </c>
@@ -14340,7 +14304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>26</v>
       </c>
@@ -14411,7 +14375,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>26</v>
       </c>
@@ -14482,7 +14446,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>26</v>
       </c>
@@ -14553,7 +14517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>26</v>
       </c>
@@ -14624,7 +14588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>26</v>
       </c>
@@ -14695,7 +14659,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>26</v>
       </c>
@@ -14766,7 +14730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>26</v>
       </c>
@@ -14837,7 +14801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>26</v>
       </c>
@@ -14908,7 +14872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>26</v>
       </c>
@@ -14979,7 +14943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>26</v>
       </c>
@@ -15050,7 +15014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>26</v>
       </c>
@@ -15121,7 +15085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>26</v>
       </c>
@@ -15192,7 +15156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>26</v>
       </c>
@@ -15263,7 +15227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>26</v>
       </c>
@@ -15334,7 +15298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>26</v>
       </c>
@@ -15405,7 +15369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>26</v>
       </c>
@@ -15476,7 +15440,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>26</v>
       </c>
@@ -15547,7 +15511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>26</v>
       </c>
@@ -15618,7 +15582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>26</v>
       </c>
@@ -15689,7 +15653,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>26</v>
       </c>
@@ -15760,7 +15724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>26</v>
       </c>
@@ -15831,7 +15795,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>26</v>
       </c>
@@ -15902,7 +15866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>26</v>
       </c>
@@ -15973,7 +15937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>26</v>
       </c>
@@ -16044,7 +16008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>26</v>
       </c>
@@ -16115,7 +16079,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>26</v>
       </c>
@@ -16186,7 +16150,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>26</v>
       </c>
@@ -16257,7 +16221,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>26</v>
       </c>
@@ -16328,7 +16292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>26</v>
       </c>
@@ -16399,7 +16363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>26</v>
       </c>
@@ -16470,7 +16434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>26</v>
       </c>
@@ -16541,7 +16505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>26</v>
       </c>
@@ -16612,7 +16576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>26</v>
       </c>
@@ -16683,7 +16647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>26</v>
       </c>
@@ -16754,7 +16718,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>26</v>
       </c>
@@ -16825,7 +16789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>26</v>
       </c>
@@ -16896,7 +16860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>26</v>
       </c>
@@ -16967,7 +16931,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>26</v>
       </c>
@@ -17038,7 +17002,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>26</v>
       </c>
@@ -17109,7 +17073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>26</v>
       </c>
@@ -17180,7 +17144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>26</v>
       </c>
@@ -17251,7 +17215,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>26</v>
       </c>
@@ -17322,7 +17286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>26</v>
       </c>
@@ -17393,7 +17357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>26</v>
       </c>
@@ -17464,7 +17428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>26</v>
       </c>
@@ -17535,7 +17499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>26</v>
       </c>
@@ -17606,7 +17570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>26</v>
       </c>
@@ -17677,7 +17641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>26</v>
       </c>
@@ -17748,7 +17712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>26</v>
       </c>
@@ -17819,7 +17783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>26</v>
       </c>
@@ -17890,7 +17854,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>26</v>
       </c>
@@ -17961,7 +17925,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>26</v>
       </c>
@@ -18032,7 +17996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>26</v>
       </c>
@@ -18103,7 +18067,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>26</v>
       </c>
@@ -18174,7 +18138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>26</v>
       </c>
@@ -18245,7 +18209,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>26</v>
       </c>
@@ -18316,7 +18280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>26</v>
       </c>
@@ -18387,7 +18351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>26</v>
       </c>
@@ -18458,7 +18422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>26</v>
       </c>
@@ -18529,7 +18493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>26</v>
       </c>
@@ -18600,7 +18564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>26</v>
       </c>
@@ -18671,7 +18635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>26</v>
       </c>
@@ -18742,7 +18706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>26</v>
       </c>
@@ -18813,7 +18777,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>26</v>
       </c>
@@ -18884,7 +18848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>26</v>
       </c>
@@ -18955,7 +18919,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>26</v>
       </c>
@@ -19026,7 +18990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>26</v>
       </c>
@@ -19097,7 +19061,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>26</v>
       </c>
@@ -19168,7 +19132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>26</v>
       </c>
@@ -19239,7 +19203,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>26</v>
       </c>
@@ -19310,7 +19274,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>26</v>
       </c>
@@ -19381,7 +19345,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>26</v>
       </c>
@@ -19452,7 +19416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>26</v>
       </c>
@@ -19523,7 +19487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>26</v>
       </c>
@@ -19594,7 +19558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>26</v>
       </c>
@@ -19665,7 +19629,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>26</v>
       </c>
@@ -19736,7 +19700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>26</v>
       </c>
@@ -19807,7 +19771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>26</v>
       </c>
@@ -19878,7 +19842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>26</v>
       </c>
@@ -19949,7 +19913,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>26</v>
       </c>
@@ -20020,7 +19984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>26</v>
       </c>
@@ -20091,7 +20055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>26</v>
       </c>
@@ -20162,7 +20126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>26</v>
       </c>
@@ -20233,7 +20197,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>26</v>
       </c>
@@ -20304,7 +20268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>26</v>
       </c>
@@ -20375,7 +20339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>26</v>
       </c>
@@ -20446,7 +20410,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>26</v>
       </c>
@@ -20517,7 +20481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>26</v>
       </c>
@@ -20588,7 +20552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>26</v>
       </c>
@@ -20659,7 +20623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>26</v>
       </c>
@@ -20730,7 +20694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>26</v>
       </c>
@@ -20801,7 +20765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>26</v>
       </c>
@@ -20872,7 +20836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>26</v>
       </c>
@@ -20943,7 +20907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>26</v>
       </c>
@@ -21014,7 +20978,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>26</v>
       </c>
@@ -21085,7 +21049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>26</v>
       </c>
@@ -21156,7 +21120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>26</v>
       </c>
@@ -21227,7 +21191,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>26</v>
       </c>
@@ -21298,7 +21262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>26</v>
       </c>
@@ -21369,7 +21333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>26</v>
       </c>
@@ -21440,7 +21404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>26</v>
       </c>
@@ -21511,7 +21475,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>26</v>
       </c>
@@ -21582,7 +21546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>26</v>
       </c>
@@ -21653,7 +21617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>26</v>
       </c>
@@ -21724,7 +21688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>26</v>
       </c>
@@ -21795,7 +21759,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>26</v>
       </c>
@@ -21866,7 +21830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>26</v>
       </c>
@@ -21937,7 +21901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>26</v>
       </c>
@@ -22008,7 +21972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>26</v>
       </c>
@@ -22079,7 +22043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>26</v>
       </c>
@@ -22150,7 +22114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>26</v>
       </c>
@@ -22221,7 +22185,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>26</v>
       </c>
@@ -22292,7 +22256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>26</v>
       </c>
@@ -22363,7 +22327,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>26</v>
       </c>
@@ -22434,7 +22398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>26</v>
       </c>
@@ -22505,7 +22469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>26</v>
       </c>
@@ -22576,7 +22540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>26</v>
       </c>
@@ -22647,7 +22611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>26</v>
       </c>
@@ -22718,7 +22682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>26</v>
       </c>
@@ -22789,7 +22753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>26</v>
       </c>
@@ -22860,7 +22824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>26</v>
       </c>
@@ -22931,7 +22895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>26</v>
       </c>
@@ -23002,7 +22966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>26</v>
       </c>
@@ -23073,7 +23037,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>26</v>
       </c>
@@ -23144,7 +23108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>26</v>
       </c>
@@ -23215,7 +23179,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>26</v>
       </c>
@@ -23286,7 +23250,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>26</v>
       </c>
@@ -23357,7 +23321,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>26</v>
       </c>
@@ -23428,7 +23392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>26</v>
       </c>
@@ -23499,7 +23463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>26</v>
       </c>
@@ -23570,7 +23534,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>26</v>
       </c>
@@ -23641,7 +23605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>26</v>
       </c>
@@ -23712,7 +23676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>26</v>
       </c>
@@ -23783,7 +23747,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>26</v>
       </c>
@@ -23854,7 +23818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>26</v>
       </c>
@@ -23925,7 +23889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>26</v>
       </c>
@@ -23996,7 +23960,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>26</v>
       </c>
@@ -24067,7 +24031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>26</v>
       </c>
@@ -24138,7 +24102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>26</v>
       </c>
@@ -24209,7 +24173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>26</v>
       </c>
@@ -24280,7 +24244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>26</v>
       </c>
@@ -24351,7 +24315,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>26</v>
       </c>
@@ -24422,7 +24386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>26</v>
       </c>
@@ -24493,7 +24457,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>26</v>
       </c>
@@ -24564,7 +24528,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>26</v>
       </c>
@@ -24635,7 +24599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>27</v>
       </c>
@@ -24706,7 +24670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>27</v>
       </c>
@@ -24777,7 +24741,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>27</v>
       </c>
@@ -24848,7 +24812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>27</v>
       </c>
@@ -24919,7 +24883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>27</v>
       </c>
@@ -24990,7 +24954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>27</v>
       </c>
@@ -25061,7 +25025,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>27</v>
       </c>
@@ -25132,7 +25096,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>27</v>
       </c>
@@ -25203,7 +25167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>27</v>
       </c>
@@ -25274,7 +25238,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>27</v>
       </c>
@@ -25345,7 +25309,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>27</v>
       </c>
@@ -25416,7 +25380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>27</v>
       </c>
@@ -25487,7 +25451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>27</v>
       </c>
@@ -25558,7 +25522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>27</v>
       </c>
@@ -25629,7 +25593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>27</v>
       </c>
@@ -25700,7 +25664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>27</v>
       </c>
@@ -25771,7 +25735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>27</v>
       </c>
@@ -25842,7 +25806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>27</v>
       </c>
@@ -25913,7 +25877,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>27</v>
       </c>
@@ -25984,7 +25948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>27</v>
       </c>
@@ -26055,7 +26019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>27</v>
       </c>
@@ -26126,7 +26090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>27</v>
       </c>
@@ -26197,7 +26161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>27</v>
       </c>
@@ -26268,7 +26232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>27</v>
       </c>
@@ -26339,7 +26303,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>27</v>
       </c>
@@ -26410,7 +26374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>27</v>
       </c>
@@ -26481,7 +26445,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>27</v>
       </c>
@@ -26552,7 +26516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>27</v>
       </c>
@@ -26623,7 +26587,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>27</v>
       </c>
@@ -26694,7 +26658,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>27</v>
       </c>
@@ -26765,7 +26729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>27</v>
       </c>
@@ -26836,7 +26800,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>27</v>
       </c>
@@ -26907,7 +26871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>27</v>
       </c>
@@ -26978,7 +26942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>27</v>
       </c>
@@ -27049,7 +27013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>27</v>
       </c>
@@ -27120,7 +27084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>27</v>
       </c>
@@ -27191,7 +27155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>27</v>
       </c>
@@ -27262,7 +27226,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>27</v>
       </c>
@@ -27333,7 +27297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>27</v>
       </c>
@@ -27404,7 +27368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>27</v>
       </c>
@@ -27475,7 +27439,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>27</v>
       </c>
@@ -27546,7 +27510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>27</v>
       </c>
@@ -27617,7 +27581,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>27</v>
       </c>
@@ -27688,7 +27652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>27</v>
       </c>
@@ -27759,7 +27723,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>27</v>
       </c>
@@ -27830,7 +27794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>27</v>
       </c>
@@ -27901,7 +27865,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>27</v>
       </c>
@@ -27972,7 +27936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>27</v>
       </c>
@@ -28043,7 +28007,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>27</v>
       </c>
@@ -28114,7 +28078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>27</v>
       </c>
@@ -28185,7 +28149,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>27</v>
       </c>
@@ -28256,7 +28220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>27</v>
       </c>
@@ -28327,7 +28291,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>27</v>
       </c>
@@ -28398,7 +28362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>27</v>
       </c>
@@ -28469,7 +28433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>27</v>
       </c>
@@ -28540,7 +28504,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>27</v>
       </c>
@@ -28611,7 +28575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>27</v>
       </c>
@@ -28682,7 +28646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>27</v>
       </c>
@@ -28753,7 +28717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>27</v>
       </c>
@@ -28824,7 +28788,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>27</v>
       </c>
@@ -28895,7 +28859,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>27</v>
       </c>
@@ -28966,7 +28930,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>27</v>
       </c>
@@ -29037,7 +29001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>27</v>
       </c>
@@ -29108,7 +29072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>27</v>
       </c>
@@ -29179,7 +29143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>27</v>
       </c>
@@ -29250,7 +29214,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>27</v>
       </c>
@@ -29321,7 +29285,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>27</v>
       </c>
@@ -29392,7 +29356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>27</v>
       </c>
@@ -29463,7 +29427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>27</v>
       </c>
@@ -29534,7 +29498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>27</v>
       </c>
@@ -29605,7 +29569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>27</v>
       </c>
@@ -29676,7 +29640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>27</v>
       </c>
@@ -29747,7 +29711,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>27</v>
       </c>
@@ -29818,7 +29782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>27</v>
       </c>
@@ -29889,7 +29853,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>27</v>
       </c>
@@ -29960,7 +29924,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>27</v>
       </c>
@@ -30031,7 +29995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>27</v>
       </c>
@@ -30102,7 +30066,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>27</v>
       </c>
@@ -30173,7 +30137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>27</v>
       </c>
@@ -30244,7 +30208,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>27</v>
       </c>
@@ -30315,7 +30279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>27</v>
       </c>
@@ -30386,7 +30350,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>27</v>
       </c>
@@ -30457,7 +30421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>27</v>
       </c>
@@ -30528,7 +30492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>27</v>
       </c>
@@ -30599,7 +30563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>27</v>
       </c>
@@ -30670,7 +30634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>27</v>
       </c>
@@ -30741,7 +30705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>27</v>
       </c>
@@ -30812,7 +30776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>27</v>
       </c>
@@ -30883,7 +30847,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>27</v>
       </c>
@@ -30954,7 +30918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>27</v>
       </c>
@@ -31025,7 +30989,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>27</v>
       </c>
@@ -31096,7 +31060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>27</v>
       </c>
@@ -31167,7 +31131,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>27</v>
       </c>
@@ -31238,7 +31202,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>27</v>
       </c>
@@ -31309,7 +31273,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>27</v>
       </c>
@@ -31380,7 +31344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>27</v>
       </c>
@@ -31451,7 +31415,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>27</v>
       </c>
@@ -31522,7 +31486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>27</v>
       </c>
@@ -31593,7 +31557,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>27</v>
       </c>
@@ -31664,7 +31628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>27</v>
       </c>
@@ -31735,7 +31699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>27</v>
       </c>
@@ -31806,7 +31770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>27</v>
       </c>
@@ -31877,7 +31841,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>27</v>
       </c>
@@ -31948,7 +31912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>27</v>
       </c>
@@ -32019,7 +31983,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>27</v>
       </c>
@@ -32090,7 +32054,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>27</v>
       </c>
@@ -32161,7 +32125,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>27</v>
       </c>
@@ -32232,7 +32196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>27</v>
       </c>
@@ -32303,7 +32267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>27</v>
       </c>
@@ -32374,7 +32338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>27</v>
       </c>
@@ -32445,7 +32409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>27</v>
       </c>
@@ -32516,7 +32480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>27</v>
       </c>
@@ -32587,7 +32551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>27</v>
       </c>
@@ -32658,7 +32622,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>27</v>
       </c>
@@ -32729,7 +32693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>27</v>
       </c>
@@ -32800,7 +32764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>27</v>
       </c>
@@ -32871,7 +32835,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>27</v>
       </c>
@@ -32942,7 +32906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>27</v>
       </c>
@@ -33013,7 +32977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>27</v>
       </c>
@@ -33084,7 +33048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>27</v>
       </c>
@@ -33155,7 +33119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>27</v>
       </c>
@@ -33226,7 +33190,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>27</v>
       </c>
@@ -33297,7 +33261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>27</v>
       </c>
@@ -33368,7 +33332,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>27</v>
       </c>
@@ -33439,7 +33403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>27</v>
       </c>
@@ -33510,7 +33474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>27</v>
       </c>
@@ -33581,7 +33545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>27</v>
       </c>
@@ -33652,7 +33616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>27</v>
       </c>
@@ -33723,7 +33687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>27</v>
       </c>
@@ -33794,7 +33758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>27</v>
       </c>
@@ -33865,7 +33829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>27</v>
       </c>
@@ -33936,7 +33900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>27</v>
       </c>
@@ -34007,7 +33971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>27</v>
       </c>
@@ -34078,7 +34042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>27</v>
       </c>
@@ -34149,7 +34113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>27</v>
       </c>
@@ -34220,7 +34184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>27</v>
       </c>
@@ -34291,7 +34255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>27</v>
       </c>
@@ -34362,7 +34326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>27</v>
       </c>
@@ -34433,7 +34397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>27</v>
       </c>
@@ -34504,7 +34468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>27</v>
       </c>
@@ -34575,7 +34539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>27</v>
       </c>
@@ -34646,7 +34610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>27</v>
       </c>
@@ -34717,7 +34681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>27</v>
       </c>
@@ -34788,7 +34752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>27</v>
       </c>
@@ -34859,7 +34823,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>27</v>
       </c>
@@ -34930,7 +34894,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>27</v>
       </c>
@@ -35001,7 +34965,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>27</v>
       </c>
@@ -35072,7 +35036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>27</v>
       </c>
@@ -35143,7 +35107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>27</v>
       </c>
@@ -35214,7 +35178,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>27</v>
       </c>
@@ -35285,7 +35249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>27</v>
       </c>
@@ -35356,7 +35320,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>27</v>
       </c>
@@ -35427,7 +35391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>27</v>
       </c>
@@ -35498,7 +35462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>27</v>
       </c>
@@ -35569,7 +35533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>27</v>
       </c>
@@ -35640,7 +35604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>27</v>
       </c>
@@ -35711,7 +35675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>27</v>
       </c>
@@ -35782,7 +35746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>27</v>
       </c>
@@ -35853,7 +35817,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>27</v>
       </c>
@@ -35924,7 +35888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>27</v>
       </c>
@@ -35995,7 +35959,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>27</v>
       </c>
@@ -36066,7 +36030,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>27</v>
       </c>
@@ -36137,7 +36101,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>27</v>
       </c>
@@ -36208,7 +36172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>27</v>
       </c>
@@ -49369,7 +49333,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>29</v>
       </c>
@@ -49446,7 +49410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>29</v>
       </c>
@@ -49523,7 +49487,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>29</v>
       </c>
@@ -49600,7 +49564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>29</v>
       </c>
@@ -49677,7 +49641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>29</v>
       </c>
@@ -49754,7 +49718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>29</v>
       </c>
@@ -49831,7 +49795,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>29</v>
       </c>
@@ -49908,7 +49872,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>29</v>
       </c>
@@ -49985,7 +49949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>29</v>
       </c>
@@ -50062,7 +50026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>29</v>
       </c>
@@ -50139,7 +50103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>29</v>
       </c>
@@ -50216,7 +50180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>29</v>
       </c>
@@ -50293,7 +50257,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>29</v>
       </c>
@@ -50370,7 +50334,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>29</v>
       </c>
@@ -50447,7 +50411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>29</v>
       </c>
@@ -50524,7 +50488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>29</v>
       </c>
@@ -50601,7 +50565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>29</v>
       </c>
@@ -50678,7 +50642,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>29</v>
       </c>
@@ -50755,7 +50719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>29</v>
       </c>
@@ -50832,7 +50796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>29</v>
       </c>
@@ -50909,7 +50873,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>29</v>
       </c>
@@ -50986,7 +50950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>29</v>
       </c>
@@ -51063,7 +51027,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>29</v>
       </c>
@@ -51140,7 +51104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>29</v>
       </c>
@@ -51217,7 +51181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>29</v>
       </c>
@@ -51294,7 +51258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>29</v>
       </c>
@@ -51371,7 +51335,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>29</v>
       </c>
@@ -51448,7 +51412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>29</v>
       </c>
@@ -51525,7 +51489,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>29</v>
       </c>
@@ -51602,7 +51566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>29</v>
       </c>
@@ -51679,7 +51643,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>29</v>
       </c>
@@ -51756,7 +51720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>29</v>
       </c>
@@ -51833,7 +51797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>29</v>
       </c>
@@ -51910,7 +51874,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>29</v>
       </c>
@@ -51987,7 +51951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>29</v>
       </c>
@@ -52064,7 +52028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>29</v>
       </c>
@@ -52141,7 +52105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>29</v>
       </c>
@@ -52218,7 +52182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>29</v>
       </c>
@@ -52295,7 +52259,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>29</v>
       </c>
@@ -52372,7 +52336,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>29</v>
       </c>
@@ -52449,7 +52413,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>29</v>
       </c>
@@ -52526,7 +52490,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>29</v>
       </c>
@@ -52603,7 +52567,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>29</v>
       </c>
@@ -52680,7 +52644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>29</v>
       </c>
@@ -52757,7 +52721,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>29</v>
       </c>
@@ -52834,7 +52798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>29</v>
       </c>
@@ -52911,7 +52875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>29</v>
       </c>
@@ -52988,7 +52952,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>29</v>
       </c>
@@ -53065,7 +53029,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>29</v>
       </c>
@@ -53142,7 +53106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>29</v>
       </c>
@@ -53219,7 +53183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>29</v>
       </c>
@@ -53296,7 +53260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>29</v>
       </c>
@@ -53373,7 +53337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>29</v>
       </c>
@@ -53450,7 +53414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>29</v>
       </c>
@@ -53527,7 +53491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>29</v>
       </c>
@@ -53604,7 +53568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>29</v>
       </c>
@@ -53681,7 +53645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>29</v>
       </c>
@@ -53758,7 +53722,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>29</v>
       </c>
@@ -53835,7 +53799,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>29</v>
       </c>
@@ -53912,7 +53876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>29</v>
       </c>
@@ -53989,7 +53953,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>29</v>
       </c>
@@ -54066,7 +54030,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>29</v>
       </c>
@@ -54143,7 +54107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>29</v>
       </c>
@@ -54220,7 +54184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>29</v>
       </c>
@@ -54297,7 +54261,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>29</v>
       </c>
@@ -54374,7 +54338,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>29</v>
       </c>
@@ -54451,7 +54415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>29</v>
       </c>
@@ -54528,7 +54492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>29</v>
       </c>
@@ -54605,7 +54569,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>29</v>
       </c>
@@ -54682,7 +54646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>29</v>
       </c>
@@ -54759,7 +54723,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>29</v>
       </c>
@@ -54836,7 +54800,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>29</v>
       </c>
@@ -54913,7 +54877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>29</v>
       </c>
@@ -54990,7 +54954,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>29</v>
       </c>
@@ -55067,7 +55031,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>29</v>
       </c>
@@ -55144,7 +55108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>29</v>
       </c>
@@ -55221,7 +55185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>29</v>
       </c>
@@ -55298,7 +55262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>29</v>
       </c>
@@ -55375,7 +55339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>29</v>
       </c>
@@ -55452,7 +55416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>29</v>
       </c>
@@ -55529,7 +55493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>29</v>
       </c>
@@ -55606,7 +55570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>29</v>
       </c>
@@ -55683,7 +55647,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>29</v>
       </c>
@@ -55760,7 +55724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>29</v>
       </c>
@@ -55837,7 +55801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>29</v>
       </c>
@@ -55914,7 +55878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>29</v>
       </c>
@@ -55991,7 +55955,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>29</v>
       </c>
@@ -56068,7 +56032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>29</v>
       </c>
@@ -56145,7 +56109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>29</v>
       </c>
@@ -56222,7 +56186,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>29</v>
       </c>
@@ -56299,7 +56263,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>29</v>
       </c>
@@ -56376,7 +56340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>29</v>
       </c>
@@ -56453,7 +56417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>29</v>
       </c>
@@ -56530,7 +56494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>29</v>
       </c>
@@ -56607,7 +56571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>29</v>
       </c>
@@ -56684,7 +56648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>29</v>
       </c>
@@ -56761,7 +56725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>29</v>
       </c>
@@ -56838,7 +56802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>29</v>
       </c>
@@ -56915,7 +56879,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>29</v>
       </c>
@@ -56992,7 +56956,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>29</v>
       </c>
@@ -57069,7 +57033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>29</v>
       </c>
@@ -57146,7 +57110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>29</v>
       </c>
@@ -57223,7 +57187,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>29</v>
       </c>
@@ -57300,7 +57264,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>29</v>
       </c>
@@ -57377,7 +57341,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>29</v>
       </c>
@@ -57454,7 +57418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>29</v>
       </c>
@@ -57531,7 +57495,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>29</v>
       </c>
@@ -57608,7 +57572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>29</v>
       </c>
@@ -57685,7 +57649,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>29</v>
       </c>
@@ -57762,7 +57726,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>29</v>
       </c>
@@ -57839,7 +57803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>29</v>
       </c>
@@ -57916,7 +57880,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>29</v>
       </c>
@@ -57993,7 +57957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>29</v>
       </c>
@@ -58070,7 +58034,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="787" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>29</v>
       </c>
@@ -58147,7 +58111,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="788" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>29</v>
       </c>
@@ -58224,7 +58188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="789" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>29</v>
       </c>
@@ -58301,7 +58265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="790" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>29</v>
       </c>
@@ -58378,7 +58342,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="791" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>29</v>
       </c>
@@ -58455,7 +58419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="792" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>29</v>
       </c>
@@ -58532,7 +58496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="793" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>29</v>
       </c>
@@ -58609,7 +58573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="794" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>29</v>
       </c>
@@ -58686,7 +58650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="795" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>29</v>
       </c>
@@ -58763,7 +58727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="796" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>29</v>
       </c>
@@ -58840,7 +58804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="797" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>29</v>
       </c>
@@ -58917,7 +58881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="798" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>29</v>
       </c>
@@ -58994,7 +58958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="799" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>29</v>
       </c>
@@ -59071,7 +59035,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="800" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>29</v>
       </c>
@@ -59148,7 +59112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="801" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>29</v>
       </c>
@@ -59225,7 +59189,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="802" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>29</v>
       </c>
@@ -59302,7 +59266,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="803" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>29</v>
       </c>
@@ -59379,7 +59343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="804" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>29</v>
       </c>
@@ -59456,7 +59420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="805" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>29</v>
       </c>
@@ -59533,7 +59497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="806" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>29</v>
       </c>
@@ -59610,7 +59574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="807" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>29</v>
       </c>
@@ -59687,7 +59651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="808" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>29</v>
       </c>
@@ -59764,7 +59728,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="809" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>29</v>
       </c>
@@ -59841,7 +59805,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="810" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>29</v>
       </c>
@@ -59918,7 +59882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="811" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>29</v>
       </c>
@@ -59995,7 +59959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="812" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>29</v>
       </c>
@@ -60072,7 +60036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="813" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>29</v>
       </c>
@@ -60149,7 +60113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="814" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>29</v>
       </c>
@@ -60226,7 +60190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="815" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>29</v>
       </c>
@@ -60303,7 +60267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="816" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>29</v>
       </c>
@@ -60380,7 +60344,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="817" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>29</v>
       </c>
@@ -60457,7 +60421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="818" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>29</v>
       </c>
@@ -60534,7 +60498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="819" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>29</v>
       </c>
@@ -60611,7 +60575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="820" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>29</v>
       </c>
@@ -60688,7 +60652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="821" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>29</v>
       </c>
@@ -60765,7 +60729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="822" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>29</v>
       </c>
@@ -60842,7 +60806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="823" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>29</v>
       </c>
@@ -60919,7 +60883,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="824" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>29</v>
       </c>
@@ -60996,7 +60960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="825" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>29</v>
       </c>
@@ -61073,7 +61037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="826" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>29</v>
       </c>
@@ -61150,7 +61114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="827" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>29</v>
       </c>
@@ -61227,7 +61191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="828" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>29</v>
       </c>
@@ -61304,7 +61268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="829" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>29</v>
       </c>
@@ -61381,7 +61345,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="830" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>29</v>
       </c>
@@ -61458,7 +61422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="831" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>29</v>
       </c>
@@ -61535,7 +61499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="832" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>29</v>
       </c>
@@ -61612,7 +61576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="833" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>29</v>
       </c>
@@ -61689,7 +61653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="834" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>29</v>
       </c>
@@ -61766,7 +61730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="835" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>29</v>
       </c>
@@ -61843,7 +61807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="836" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>29</v>
       </c>
@@ -61920,7 +61884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="837" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>29</v>
       </c>
@@ -61997,7 +61961,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="838" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>29</v>
       </c>
@@ -62074,7 +62038,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="839" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>29</v>
       </c>
@@ -62151,7 +62115,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="840" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>29</v>
       </c>
@@ -62228,7 +62192,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="841" spans="1:25" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>29</v>
       </c>
@@ -62306,13 +62270,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y841" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="PRD85_PR40_CPent_UD050_UR045_PE60_I0"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Y841"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>